--- a/INVENTORY ALERT SYSTEM.xlsx
+++ b/INVENTORY ALERT SYSTEM.xlsx
@@ -4,21 +4,25 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="60" windowWidth="22932" windowHeight="9504" activeTab="4"/>
+    <workbookView xWindow="96" yWindow="60" windowWidth="22932" windowHeight="9504"/>
   </bookViews>
   <sheets>
     <sheet name="INVENTORY ALERT SYSTEM DATA" sheetId="1" r:id="rId1"/>
-    <sheet name="DASHBOARD PREVIEW" sheetId="2" r:id="rId2"/>
-    <sheet name="EXECUTIVE SUMMARY" sheetId="3" r:id="rId3"/>
-    <sheet name="RECOMMENDATIONS" sheetId="4" r:id="rId4"/>
+    <sheet name="PIVOT TABLE" sheetId="9" r:id="rId2"/>
+    <sheet name="DASHBOARD PREVIEW" sheetId="2" r:id="rId3"/>
+    <sheet name="EXECUTIVE SUMMARY" sheetId="3" r:id="rId4"/>
     <sheet name="KPI INDICATOR" sheetId="5" r:id="rId5"/>
+    <sheet name="RECOMMENDATIONS" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <pivotCaches>
+    <pivotCache cacheId="1" r:id="rId7"/>
+  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
   <si>
     <t>SKU</t>
   </si>
@@ -96,18 +100,6 @@
   </si>
   <si>
     <t>USB Cable</t>
-  </si>
-  <si>
-    <t>TOTAL STOCK0NHAND</t>
-  </si>
-  <si>
-    <t>TOTAL REORDER LEVEL</t>
-  </si>
-  <si>
-    <t>TOTAL SAFETY STOCK</t>
-  </si>
-  <si>
-    <t>TOTAL MONTHLY DEMAND</t>
   </si>
   <si>
     <t>Inventory Optimization &amp; Reorder Alert System</t>
@@ -410,34 +402,64 @@
     <t>9.8 days</t>
   </si>
   <si>
-    <t>⚠️ Below target (14 days)</t>
-  </si>
-  <si>
     <t>Average Turnover Ratio</t>
   </si>
   <si>
     <t>2.72x/month</t>
   </si>
   <si>
-    <t>✅ Healthy</t>
-  </si>
-  <si>
     <t>SKUs Below Reorder Level</t>
   </si>
   <si>
     <t>4 of 8</t>
   </si>
   <si>
-    <t>🔴 Critical</t>
-  </si>
-  <si>
     <t>SKUs with Negative Safety Buffer</t>
   </si>
   <si>
     <t>Critical SKUs (&lt;3 days to stockout)</t>
   </si>
   <si>
-    <t>🔴 URGENT</t>
+    <t xml:space="preserve"> Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Healthy</t>
+  </si>
+  <si>
+    <t>Below target (14 days)</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>URGENT</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of StockOnHand</t>
+  </si>
+  <si>
+    <t>Sum of SafetyStock</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
+    <t>Sum of ReorderLevel</t>
+  </si>
+  <si>
+    <t>Sum of LeadTimeDays</t>
+  </si>
+  <si>
+    <t>Sum of MonthlyDemand</t>
+  </si>
+  <si>
+    <t>PIVOT TABLE</t>
   </si>
 </sst>
 </file>
@@ -574,7 +596,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -642,6 +664,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -791,10 +818,6 @@
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D124-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
 </file>
 
-<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D124-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
-</file>
-
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
@@ -964,24 +987,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="86406656"/>
-        <c:axId val="133391488"/>
+        <c:axId val="97737728"/>
+        <c:axId val="99983360"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86406656"/>
+        <c:axId val="97737728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="133391488"/>
+        <c:crossAx val="99983360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="133391488"/>
+        <c:axId val="99983360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -989,20 +1012,19 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="86406656"/>
+        <c:crossAx val="97737728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageMargins b="0.750000000000001" l="0.70000000000000062" r="0.70000000000000062" t="0.750000000000001" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1177,24 +1199,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="46725376"/>
-        <c:axId val="47067136"/>
+        <c:axId val="97945856"/>
+        <c:axId val="97959936"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46725376"/>
+        <c:axId val="97945856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="47067136"/>
+        <c:crossAx val="97959936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47067136"/>
+        <c:axId val="97959936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1202,20 +1224,19 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="46725376"/>
+        <c:crossAx val="97945856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageMargins b="0.750000000000001" l="0.70000000000000062" r="0.70000000000000062" t="0.750000000000001" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1225,9 +1246,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:chart>
-    <c:title>
-      <c:layout/>
-    </c:title>
+    <c:title/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -1314,23 +1333,24 @@
           </c:val>
         </c:ser>
         <c:gapWidth val="100"/>
-        <c:axId val="46716032"/>
-        <c:axId val="87781376"/>
+        <c:axId val="97967104"/>
+        <c:axId val="97968896"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46716032"/>
+        <c:axId val="97967104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="87781376"/>
+        <c:crossAx val="97968896"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87781376"/>
+        <c:axId val="97968896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1338,19 +1358,19 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="46716032"/>
+        <c:crossAx val="97967104"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageMargins b="0.750000000000001" l="0.70000000000000062" r="0.70000000000000062" t="0.750000000000001" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1525,24 +1545,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="47447424"/>
-        <c:axId val="131480576"/>
+        <c:axId val="98055296"/>
+        <c:axId val="98056832"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="47447424"/>
+        <c:axId val="98055296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="131480576"/>
+        <c:crossAx val="98056832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="131480576"/>
+        <c:axId val="98056832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1550,20 +1570,19 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="47447424"/>
+        <c:crossAx val="98055296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageMargins b="0.750000000000001" l="0.70000000000000062" r="0.70000000000000062" t="0.750000000000001" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1573,9 +1592,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:chart>
-    <c:title>
-      <c:layout/>
-    </c:title>
+    <c:title/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -1661,24 +1678,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="139828224"/>
-        <c:axId val="140093312"/>
+        <c:axId val="98080640"/>
+        <c:axId val="98082176"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="139828224"/>
+        <c:axId val="98080640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="140093312"/>
+        <c:crossAx val="98082176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="140093312"/>
+        <c:axId val="98082176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1686,20 +1703,19 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="139828224"/>
+        <c:crossAx val="98080640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageMargins b="0.75000000000000089" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000089" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1860,18 +1876,264 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="HP" refreshedDate="46180.275929050928" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="8">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="SKU" numFmtId="0">
+      <sharedItems count="8">
+        <s v="SKU001"/>
+        <s v="SKU002"/>
+        <s v="SKU003"/>
+        <s v="SKU004"/>
+        <s v="SKU005"/>
+        <s v="SKU006"/>
+        <s v="SKU007"/>
+        <s v="SKU008"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="ProductName" numFmtId="0">
+      <sharedItems count="8">
+        <s v="Laptop Pro"/>
+        <s v="Phone X"/>
+        <s v="Tablet Lite"/>
+        <s v="Wireless Mouse"/>
+        <s v="Keyboard"/>
+        <s v="Monitor 24"/>
+        <s v="Desk Mat"/>
+        <s v="USB Cable"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Electronics"/>
+        <s v="Accessories"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="StockOnHand" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="8" maxValue="500"/>
+    </cacheField>
+    <cacheField name="ReorderLevel" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15" maxValue="100"/>
+    </cacheField>
+    <cacheField name="SafetyStock" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="8" maxValue="50"/>
+    </cacheField>
+    <cacheField name="LeadTimeDays" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="14"/>
+    </cacheField>
+    <cacheField name="MonthlyDemand" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="90" maxValue="1200"/>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="8">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="45"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="12"/>
+    <n v="25"/>
+    <n v="15"/>
+    <n v="4"/>
+    <n v="180"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="30"/>
+    <n v="15"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="90"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="150"/>
+    <n v="50"/>
+    <n v="25"/>
+    <n v="7"/>
+    <n v="400"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="25"/>
+    <n v="30"/>
+    <n v="10"/>
+    <n v="6"/>
+    <n v="200"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="8"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="8"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="200"/>
+    <n v="40"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="500"/>
+    <n v="100"/>
+    <n v="50"/>
+    <n v="14"/>
+    <n v="1200"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:F14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+  </colItems>
+  <dataFields count="5">
+    <dataField name="Sum of StockOnHand" fld="3" baseField="0" baseItem="0"/>
+    <dataField name="Sum of SafetyStock" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Sum of ReorderLevel" fld="4" baseField="0" baseItem="0"/>
+    <dataField name="Sum of LeadTimeDays" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Sum of MonthlyDemand" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H10" totalsRowShown="0" headerRowDxfId="9" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H10" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A2:H10"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="SKU" dataDxfId="8"/>
-    <tableColumn id="2" name="ProductName" dataDxfId="7"/>
-    <tableColumn id="3" name="Category" dataDxfId="6"/>
-    <tableColumn id="4" name="StockOnHand" dataDxfId="5"/>
-    <tableColumn id="5" name="ReorderLevel" dataDxfId="4"/>
-    <tableColumn id="6" name="SafetyStock" dataDxfId="3"/>
-    <tableColumn id="7" name="LeadTimeDays" dataDxfId="2"/>
-    <tableColumn id="8" name="MonthlyDemand" dataDxfId="1"/>
+    <tableColumn id="1" name="SKU" dataDxfId="7"/>
+    <tableColumn id="2" name="ProductName" dataDxfId="6"/>
+    <tableColumn id="3" name="Category" dataDxfId="5"/>
+    <tableColumn id="4" name="StockOnHand" dataDxfId="4"/>
+    <tableColumn id="5" name="ReorderLevel" dataDxfId="3"/>
+    <tableColumn id="6" name="SafetyStock" dataDxfId="2"/>
+    <tableColumn id="7" name="LeadTimeDays" dataDxfId="1"/>
+    <tableColumn id="8" name="MonthlyDemand" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium24" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2179,7 +2441,7 @@
       <c r="A1"/>
       <c r="B1"/>
       <c r="C1" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D1"/>
       <c r="E1"/>
@@ -2432,44 +2694,24 @@
       <c r="H11" s="20"/>
     </row>
     <row r="13" spans="1:8" ht="18">
-      <c r="A13" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="2">
-        <f>SUM(D3:D10)</f>
-        <v>970</v>
-      </c>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:8" ht="18">
-      <c r="A14" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="2">
-        <f>SUM(E3:E10)</f>
-        <v>300</v>
-      </c>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:8" ht="18">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="2">
-        <f>SUM(F3:F10)</f>
-        <v>150</v>
-      </c>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="18">
-      <c r="A16" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="2">
-        <f>SUM(H3:H10)</f>
-        <v>2640</v>
-      </c>
+      <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:2" ht="18">
       <c r="A17" s="3"/>
@@ -2486,18 +2728,247 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:F14"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" ht="21">
+      <c r="C2" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" s="31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="33">
+        <v>200</v>
+      </c>
+      <c r="C6" s="33">
+        <v>20</v>
+      </c>
+      <c r="D6" s="33">
+        <v>40</v>
+      </c>
+      <c r="E6" s="33">
+        <v>10</v>
+      </c>
+      <c r="F6" s="33">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="33">
+        <v>25</v>
+      </c>
+      <c r="C7" s="33">
+        <v>10</v>
+      </c>
+      <c r="D7" s="33">
+        <v>30</v>
+      </c>
+      <c r="E7" s="33">
+        <v>6</v>
+      </c>
+      <c r="F7" s="33">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="33">
+        <v>45</v>
+      </c>
+      <c r="C8" s="33">
+        <v>10</v>
+      </c>
+      <c r="D8" s="33">
+        <v>20</v>
+      </c>
+      <c r="E8" s="33">
+        <v>5</v>
+      </c>
+      <c r="F8" s="33">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="33">
+        <v>8</v>
+      </c>
+      <c r="C9" s="33">
+        <v>12</v>
+      </c>
+      <c r="D9" s="33">
+        <v>20</v>
+      </c>
+      <c r="E9" s="33">
+        <v>8</v>
+      </c>
+      <c r="F9" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="33">
+        <v>12</v>
+      </c>
+      <c r="C10" s="33">
+        <v>15</v>
+      </c>
+      <c r="D10" s="33">
+        <v>25</v>
+      </c>
+      <c r="E10" s="33">
+        <v>4</v>
+      </c>
+      <c r="F10" s="33">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="33">
+        <v>30</v>
+      </c>
+      <c r="C11" s="33">
+        <v>8</v>
+      </c>
+      <c r="D11" s="33">
+        <v>15</v>
+      </c>
+      <c r="E11" s="33">
+        <v>3</v>
+      </c>
+      <c r="F11" s="33">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="33">
+        <v>500</v>
+      </c>
+      <c r="C12" s="33">
+        <v>50</v>
+      </c>
+      <c r="D12" s="33">
+        <v>100</v>
+      </c>
+      <c r="E12" s="33">
+        <v>14</v>
+      </c>
+      <c r="F12" s="33">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="33">
+        <v>150</v>
+      </c>
+      <c r="C13" s="33">
+        <v>25</v>
+      </c>
+      <c r="D13" s="33">
+        <v>50</v>
+      </c>
+      <c r="E13" s="33">
+        <v>7</v>
+      </c>
+      <c r="F13" s="33">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="33">
+        <v>970</v>
+      </c>
+      <c r="C14" s="33">
+        <v>150</v>
+      </c>
+      <c r="D14" s="33">
+        <v>300</v>
+      </c>
+      <c r="E14" s="33">
+        <v>57</v>
+      </c>
+      <c r="F14" s="33">
+        <v>2640</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B19:M55"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="19" spans="2:13" ht="21">
       <c r="B19" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
@@ -2505,15 +2976,15 @@
     </row>
     <row r="37" spans="2:11" ht="21">
       <c r="B37" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="3:3" ht="21">
       <c r="C55" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2522,19 +2993,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:P25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2" spans="1:16" ht="21">
       <c r="C2" s="13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2554,7 +3025,7 @@
     </row>
     <row r="4" spans="1:16" ht="18">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2574,7 +3045,7 @@
     </row>
     <row r="5" spans="1:16" ht="18">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2594,7 +3065,7 @@
     </row>
     <row r="6" spans="1:16" ht="18">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2614,7 +3085,7 @@
     </row>
     <row r="7" spans="1:16" ht="18">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2634,7 +3105,7 @@
     </row>
     <row r="8" spans="1:16" ht="18">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2654,7 +3125,7 @@
     </row>
     <row r="9" spans="1:16" ht="18">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2694,7 +3165,7 @@
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -2712,7 +3183,7 @@
     </row>
     <row r="12" spans="1:16" ht="18">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2750,7 +3221,7 @@
     </row>
     <row r="14" spans="1:16" ht="18">
       <c r="A14" s="22" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2788,7 +3259,7 @@
     </row>
     <row r="16" spans="1:16" ht="18">
       <c r="A16" s="22" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2826,7 +3297,7 @@
     </row>
     <row r="18" spans="1:16" ht="18">
       <c r="A18" s="22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2864,7 +3335,7 @@
     </row>
     <row r="20" spans="1:16" ht="18">
       <c r="A20" s="22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2920,7 +3391,7 @@
     </row>
     <row r="23" spans="1:16" ht="18">
       <c r="A23" s="22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2976,207 +3447,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:G15"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="27.44140625" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" customWidth="1"/>
-    <col min="4" max="4" width="21.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:7" ht="23.4">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:7" ht="23.4">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-    </row>
-    <row r="4" spans="1:7" ht="42">
-      <c r="A4" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:7" ht="63">
-      <c r="A5" s="16">
-        <v>1</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:7" ht="42">
-      <c r="A6" s="16">
-        <v>2</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:7" ht="63">
-      <c r="A7" s="16">
-        <v>3</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:7" ht="63">
-      <c r="A8" s="16">
-        <v>4</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9" spans="1:7" ht="84">
-      <c r="A9" s="16">
-        <v>5</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:7" ht="21">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:7" ht="21">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:7" ht="21">
-      <c r="A12" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:7" ht="21">
-      <c r="A13" s="18"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:7" ht="21">
-      <c r="A14" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" spans="1:7" ht="21">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <controls>
-    <control shapeId="2049" r:id="rId3" name="Control 1"/>
-  </controls>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet2"/>
@@ -3190,106 +3460,106 @@
   <sheetData>
     <row r="1" spans="1:3" ht="23.4">
       <c r="A1" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21">
       <c r="A3" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18">
       <c r="A4" s="30" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B4" s="30">
         <v>8</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18">
       <c r="A5" s="30" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18">
       <c r="A6" s="30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36">
       <c r="A7" s="30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18">
       <c r="A8" s="30" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C8" s="30" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="36">
+    <row r="9" spans="1:3" ht="18">
       <c r="A9" s="30" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B9" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18">
+      <c r="A10" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="36">
-      <c r="A10" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="36">
+    </row>
+    <row r="11" spans="1:3" ht="18">
       <c r="A11" s="30" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B11" s="30">
         <v>2</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="23.4">
@@ -3985,4 +4255,190 @@
     <control shapeId="5121" r:id="rId2" name="Control 1"/>
   </controls>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="39.44140625" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="38.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="23.4">
+      <c r="A1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="23.4">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="21">
+      <c r="A3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" ht="42">
+      <c r="A4" s="16">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="21">
+      <c r="A5" s="16">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="42">
+      <c r="A6" s="16">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="21">
+      <c r="A7" s="16">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" ht="42">
+      <c r="A8" s="16">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" ht="21">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" ht="21">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" ht="21">
+      <c r="A11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" ht="21">
+      <c r="A12" s="18"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:7" ht="21">
+      <c r="A13" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>